--- a/Dashboards/data/Data final/empleo/empleo adecuado/variacion_empleo_significancia.xlsx
+++ b/Dashboards/data/Data final/empleo/empleo adecuado/variacion_empleo_significancia.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
   <si>
     <t>anio</t>
   </si>
   <si>
-    <t>anio_anterior</t>
+    <t>anioAnterior</t>
   </si>
   <si>
     <t>indicador</t>
@@ -33,19 +33,22 @@
     <t>se</t>
   </si>
   <si>
-    <t>valor_anterior</t>
-  </si>
-  <si>
-    <t>se_anterior</t>
-  </si>
-  <si>
-    <t>variacion_pp</t>
-  </si>
-  <si>
-    <t>t_stat</t>
-  </si>
-  <si>
-    <t>p_value</t>
+    <t>valorAnterior</t>
+  </si>
+  <si>
+    <t>seAnterior</t>
+  </si>
+  <si>
+    <t>variacionPp</t>
+  </si>
+  <si>
+    <t>variacionPct</t>
+  </si>
+  <si>
+    <t>tStat</t>
+  </si>
+  <si>
+    <t>pValue</t>
   </si>
   <si>
     <t>significativo</t>
@@ -54,10 +57,10 @@
     <t>Sí (p&lt;0.01)</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Sí (p&lt;0.05)</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -103,7 +106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -140,6 +143,9 @@
       <c r="K1" t="s">
         <v>11</v>
       </c>
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -152,28 +158,31 @@
         <v>3</v>
       </c>
       <c r="D2" s="1">
-        <v>44.768524169921875</v>
+        <v>44.768500000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>0.26409822702407837</v>
+        <v>0.69269999999999998</v>
       </c>
       <c r="F2" s="1">
-        <v>43.199901580810547</v>
+        <v>43.1999</v>
       </c>
       <c r="G2" s="1">
-        <v>0.26285862922668457</v>
+        <v>0.70190000000000008</v>
       </c>
       <c r="H2" s="1">
-        <v>1.5686225891113281</v>
+        <v>1.5686</v>
       </c>
       <c r="I2" s="1">
-        <v>4.2097587585449219</v>
+        <v>3.6311</v>
       </c>
       <c r="J2" s="1">
-        <v>2.5564349925843999e-05</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
+        <v>3.0077000000000003</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.0027000000000000001</v>
+      </c>
+      <c r="L2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -187,28 +196,31 @@
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>39.177207946777344</v>
+        <v>39.177199999999999</v>
       </c>
       <c r="E3" s="1">
-        <v>0.25738289952278137</v>
+        <v>0.63140000000000007</v>
       </c>
       <c r="F3" s="1">
-        <v>44.768524169921875</v>
+        <v>44.768500000000003</v>
       </c>
       <c r="G3" s="1">
-        <v>0.26409822702407837</v>
+        <v>0.69259999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>-5.5913162231445312</v>
+        <v>-5.5913000000000004</v>
       </c>
       <c r="I3" s="1">
-        <v>-15.161929130554199</v>
+        <v>-12.4894</v>
       </c>
       <c r="J3" s="1">
+        <v>-5.9674000000000005</v>
+      </c>
+      <c r="K3" s="1">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
-        <v>12</v>
+      <c r="L3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -222,28 +234,31 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>44.677097320556641</v>
+        <v>44.677100000000003</v>
       </c>
       <c r="E4" s="1">
-        <v>0.25879991054534912</v>
+        <v>0.66849999999999998</v>
       </c>
       <c r="F4" s="1">
-        <v>39.177207946777344</v>
+        <v>39.177199999999999</v>
       </c>
       <c r="G4" s="1">
-        <v>0.25738289952278137</v>
+        <v>0.63150000000000006</v>
       </c>
       <c r="H4" s="1">
-        <v>5.4998893737792969</v>
+        <v>5.4999000000000002</v>
       </c>
       <c r="I4" s="1">
-        <v>15.068283081054688</v>
+        <v>14.038500000000001</v>
       </c>
       <c r="J4" s="1">
+        <v>9.8693000000000008</v>
+      </c>
+      <c r="K4" s="1">
         <v>0</v>
       </c>
-      <c r="K4" t="s">
-        <v>12</v>
+      <c r="L4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -257,28 +272,31 @@
         <v>3</v>
       </c>
       <c r="D5" s="1">
-        <v>45.529296875</v>
+        <v>45.529299999999999</v>
       </c>
       <c r="E5" s="1">
-        <v>0.28245645761489868</v>
+        <v>0.73940000000000006</v>
       </c>
       <c r="F5" s="1">
-        <v>44.677097320556641</v>
+        <v>44.677100000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>0.25879991054534912</v>
+        <v>0.66839999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>0.85219955444335938</v>
+        <v>0.85220000000000007</v>
       </c>
       <c r="I5" s="1">
-        <v>2.2245330810546875</v>
+        <v>1.9075000000000002</v>
       </c>
       <c r="J5" s="1">
-        <v>0.026112599298357964</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
+        <v>0.85510000000000008</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.3926</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -292,28 +310,31 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>46.532867431640625</v>
+        <v>46.532900000000005</v>
       </c>
       <c r="E6" s="1">
-        <v>0.27444121241569519</v>
+        <v>0.70510000000000006</v>
       </c>
       <c r="F6" s="1">
-        <v>45.529296875</v>
+        <v>45.529299999999999</v>
       </c>
       <c r="G6" s="1">
-        <v>0.28245645761489868</v>
+        <v>0.73950000000000005</v>
       </c>
       <c r="H6" s="1">
-        <v>1.003570556640625</v>
+        <v>1.0036</v>
       </c>
       <c r="I6" s="1">
-        <v>2.5482528209686279</v>
+        <v>2.2042000000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>0.010826397687196732</v>
-      </c>
-      <c r="K6" t="s">
-        <v>13</v>
+        <v>1.4021000000000001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.161</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -327,28 +348,31 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>47.865016937255859</v>
+        <v>47.865000000000002</v>
       </c>
       <c r="E7" s="1">
-        <v>0.26573744416236877</v>
+        <v>0.72910000000000008</v>
       </c>
       <c r="F7" s="1">
-        <v>46.532867431640625</v>
+        <v>46.532900000000005</v>
       </c>
       <c r="G7" s="1">
-        <v>0.27444121241569519</v>
+        <v>0.70500000000000007</v>
       </c>
       <c r="H7" s="1">
-        <v>1.3321495056152344</v>
+        <v>1.3322000000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>3.4871785640716553</v>
+        <v>2.8628</v>
       </c>
       <c r="J7" s="1">
-        <v>0.0004881453060079366</v>
-      </c>
-      <c r="K7" t="s">
-        <v>12</v>
+        <v>1.3140000000000001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.18890000000000001</v>
+      </c>
+      <c r="L7" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -362,28 +386,31 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>49.284751892089844</v>
+        <v>49.284800000000004</v>
       </c>
       <c r="E8" s="1">
-        <v>0.21687968075275421</v>
+        <v>0.68059999999999998</v>
       </c>
       <c r="F8" s="1">
-        <v>47.865016937255859</v>
+        <v>47.865000000000002</v>
       </c>
       <c r="G8" s="1">
-        <v>0.26573744416236877</v>
+        <v>0.72920000000000007</v>
       </c>
       <c r="H8" s="1">
-        <v>1.4197349548339844</v>
+        <v>1.4197</v>
       </c>
       <c r="I8" s="1">
-        <v>4.1390953063964844</v>
+        <v>2.9661</v>
       </c>
       <c r="J8" s="1">
-        <v>3.4867807698901743e-05</v>
-      </c>
-      <c r="K8" t="s">
-        <v>12</v>
+        <v>1.8500000000000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.064399999999999999</v>
+      </c>
+      <c r="L8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -397,28 +424,31 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>46.503925323486328</v>
+        <v>46.503900000000002</v>
       </c>
       <c r="E9" s="1">
-        <v>0.21829380095005035</v>
+        <v>0.62050000000000005</v>
       </c>
       <c r="F9" s="1">
-        <v>49.284751892089844</v>
+        <v>49.284800000000004</v>
       </c>
       <c r="G9" s="1">
-        <v>0.21687968075275421</v>
+        <v>0.68059999999999998</v>
       </c>
       <c r="H9" s="1">
-        <v>-2.7808265686035156</v>
+        <v>-2.7808000000000002</v>
       </c>
       <c r="I9" s="1">
-        <v>-9.0369977951049805</v>
+        <v>-5.6424000000000003</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>12</v>
+        <v>-4.0587</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.0001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -432,28 +462,31 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>41.189304351806641</v>
+        <v>41.189800000000005</v>
       </c>
       <c r="E10" s="1">
-        <v>0.21005174517631531</v>
+        <v>0.48100000000000004</v>
       </c>
       <c r="F10" s="1">
-        <v>46.503925323486328</v>
+        <v>46.503900000000002</v>
       </c>
       <c r="G10" s="1">
-        <v>0.21829380095005035</v>
+        <v>0.62050000000000005</v>
       </c>
       <c r="H10" s="1">
-        <v>-5.3146209716796875</v>
+        <v>-5.3140999999999998</v>
       </c>
       <c r="I10" s="1">
-        <v>-17.543355941772461</v>
+        <v>-11.427300000000001</v>
       </c>
       <c r="J10" s="1">
+        <v>-6.7692000000000005</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>12</v>
+      <c r="L10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -467,28 +500,31 @@
         <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>42.263946533203125</v>
+        <v>42.2639</v>
       </c>
       <c r="E11" s="1">
-        <v>0.21255508065223694</v>
+        <v>0.5625</v>
       </c>
       <c r="F11" s="1">
-        <v>41.189304351806641</v>
+        <v>41.189800000000005</v>
       </c>
       <c r="G11" s="1">
-        <v>0.21005174517631531</v>
+        <v>0.5161</v>
       </c>
       <c r="H11" s="1">
-        <v>1.0746421813964844</v>
+        <v>1.0741000000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>3.5961248874664307</v>
+        <v>2.6078000000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>0.00032299276790581644</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
+        <v>1.5199</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.12860000000000002</v>
+      </c>
+      <c r="L11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -502,28 +538,31 @@
         <v>3</v>
       </c>
       <c r="D12" s="1">
-        <v>40.638175964355469</v>
+        <v>40.638200000000005</v>
       </c>
       <c r="E12" s="1">
-        <v>0.28715291619300842</v>
+        <v>0.57420000000000004</v>
       </c>
       <c r="F12" s="1">
-        <v>42.263946533203125</v>
+        <v>42.2639</v>
       </c>
       <c r="G12" s="1">
-        <v>0.21255508065223694</v>
+        <v>0.53590000000000004</v>
       </c>
       <c r="H12" s="1">
-        <v>-1.6257705688476562</v>
+        <v>-1.6258000000000001</v>
       </c>
       <c r="I12" s="1">
-        <v>-4.5506339073181152</v>
+        <v>-3.8467000000000002</v>
       </c>
       <c r="J12" s="1">
-        <v>5.348453669284936e-06</v>
-      </c>
-      <c r="K12" t="s">
-        <v>12</v>
+        <v>-2.0710000000000002</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.038400000000000004</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -537,28 +576,31 @@
         <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>38.847827911376953</v>
+        <v>38.847799999999999</v>
       </c>
       <c r="E13" s="1">
-        <v>0.28424543142318726</v>
+        <v>0.65850000000000009</v>
       </c>
       <c r="F13" s="1">
-        <v>40.638175964355469</v>
+        <v>40.638200000000005</v>
       </c>
       <c r="G13" s="1">
-        <v>0.28715291619300842</v>
+        <v>0.56710000000000005</v>
       </c>
       <c r="H13" s="1">
-        <v>-1.7903480529785156</v>
+        <v>-1.7903</v>
       </c>
       <c r="I13" s="1">
-        <v>-4.4310622215270996</v>
+        <v>-4.4056000000000006</v>
       </c>
       <c r="J13" s="1">
-        <v>9.3770022431272082e-06</v>
-      </c>
-      <c r="K13" t="s">
-        <v>12</v>
+        <v>-3.0700000000000003</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.0022000000000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -572,28 +614,31 @@
         <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>30.848476409912109</v>
+        <v>30.848500000000001</v>
       </c>
       <c r="E14" s="1">
-        <v>0.37381359934806824</v>
+        <v>0.84470000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>38.847827911376953</v>
+        <v>38.847799999999999</v>
       </c>
       <c r="G14" s="1">
-        <v>0.28424543142318726</v>
+        <v>0.69420000000000004</v>
       </c>
       <c r="H14" s="1">
-        <v>-7.9993515014648438</v>
+        <v>-7.9994000000000005</v>
       </c>
       <c r="I14" s="1">
-        <v>-17.034088134765625</v>
+        <v>-20.5915</v>
       </c>
       <c r="J14" s="1">
+        <v>-6.8873000000000006</v>
+      </c>
+      <c r="K14" s="1">
         <v>0</v>
       </c>
-      <c r="K14" t="s">
-        <v>12</v>
+      <c r="L14" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -607,28 +652,31 @@
         <v>3</v>
       </c>
       <c r="D15" s="1">
-        <v>33.683444976806641</v>
+        <v>33.940899999999999</v>
       </c>
       <c r="E15" s="1">
-        <v>0.21851661801338196</v>
+        <v>1.1606000000000001</v>
       </c>
       <c r="F15" s="1">
-        <v>30.848476409912109</v>
+        <v>30.848500000000001</v>
       </c>
       <c r="G15" s="1">
-        <v>0.37381359934806824</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="H15" s="1">
-        <v>2.8349685668945312</v>
+        <v>3.0924</v>
       </c>
       <c r="I15" s="1">
-        <v>6.5473217964172363</v>
+        <v>10.0244</v>
       </c>
       <c r="J15" s="1">
-        <v>5.8578031314482359e-11</v>
-      </c>
-      <c r="K15" t="s">
-        <v>12</v>
+        <v>2.0661</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.038900000000000004</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -642,28 +690,31 @@
         <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>35.518550872802734</v>
+        <v>36.035600000000002</v>
       </c>
       <c r="E16" s="1">
-        <v>0.2263176292181015</v>
+        <v>1.2565</v>
       </c>
       <c r="F16" s="1">
-        <v>33.683444976806641</v>
+        <v>33.940899999999999</v>
       </c>
       <c r="G16" s="1">
-        <v>0.21851661801338196</v>
+        <v>1.1172</v>
       </c>
       <c r="H16" s="1">
-        <v>1.8351058959960938</v>
+        <v>2.0948000000000002</v>
       </c>
       <c r="I16" s="1">
-        <v>5.8332571983337402</v>
+        <v>6.1718999999999999</v>
       </c>
       <c r="J16" s="1">
-        <v>5.4355684397933146e-09</v>
-      </c>
-      <c r="K16" t="s">
-        <v>12</v>
+        <v>1.7427000000000001</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.081600000000000006</v>
+      </c>
+      <c r="L16" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -677,27 +728,30 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>36.039699554443359</v>
+        <v>35.916800000000002</v>
       </c>
       <c r="E17" s="1">
-        <v>0.23088085651397705</v>
+        <v>1.2511000000000001</v>
       </c>
       <c r="F17" s="1">
-        <v>35.518550872802734</v>
+        <v>36.035600000000002</v>
       </c>
       <c r="G17" s="1">
-        <v>0.2263176292181015</v>
+        <v>1.2987</v>
       </c>
       <c r="H17" s="1">
-        <v>0.521148681640625</v>
+        <v>-0.1188</v>
       </c>
       <c r="I17" s="1">
-        <v>1.6119450330734253</v>
+        <v>-0.3296</v>
       </c>
       <c r="J17" s="1">
-        <v>0.10697390139102936</v>
-      </c>
-      <c r="K17" t="s">
+        <v>-0.062400000000000004</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.95030000000000003</v>
+      </c>
+      <c r="L17" t="s">
         <v>14</v>
       </c>
     </row>
@@ -712,28 +766,31 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>34.134254455566406</v>
+        <v>33.0291</v>
       </c>
       <c r="E18" s="1">
-        <v>0.22983385622501373</v>
+        <v>1.7388000000000001</v>
       </c>
       <c r="F18" s="1">
-        <v>36.039699554443359</v>
+        <v>35.916800000000002</v>
       </c>
       <c r="G18" s="1">
-        <v>0.23088085651397705</v>
+        <v>1.2116</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.9054450988769531</v>
+        <v>-2.8877999999999999</v>
       </c>
       <c r="I18" s="1">
-        <v>-5.8489542007446289</v>
+        <v>-8.0402000000000005</v>
       </c>
       <c r="J18" s="1">
-        <v>4.9467328011587597e-09</v>
-      </c>
-      <c r="K18" t="s">
-        <v>12</v>
+        <v>-2.0235000000000003</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.043200000000000002</v>
+      </c>
+      <c r="L18" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -747,28 +804,31 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>36.787342071533203</v>
+        <v>37.068800000000003</v>
       </c>
       <c r="E19" s="1">
-        <v>0.2343364804983139</v>
+        <v>1.6704000000000001</v>
       </c>
       <c r="F19" s="1">
-        <v>34.134254455566406</v>
+        <v>33.0291</v>
       </c>
       <c r="G19" s="1">
-        <v>0.22983385622501373</v>
+        <v>1.7568000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>2.6530876159667969</v>
+        <v>4.0396999999999998</v>
       </c>
       <c r="I19" s="1">
-        <v>8.0829296112060547</v>
+        <v>12.2309</v>
       </c>
       <c r="J19" s="1">
-        <v>6.6613381477509392e-16</v>
-      </c>
-      <c r="K19" t="s">
-        <v>12</v>
+        <v>1.6323000000000001</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0.1028</v>
+      </c>
+      <c r="L19" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
